--- a/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
+++ b/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Venda R$ 100.000,00 credito aprovada</t>
+          <t>Venda de R$ 100.000,00 (valor maximo da automacao) no credito, aprovada. 030-000 = TRANSACAO AUTORIZADA, autorizacao 094787, NSU 741684.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Venda a vista R$ 5,00 (aVista=true, autorizador C6PAY pre-selecionado)</t>
+          <t>Venda a vista de R$ 5,00 no credito, aprovada (quantidadeParcelas = 1 e aVista = true na intencao). 030-000 = TRANSACAO AUTORIZADA, autorizacao 094787, NSU 741686. O comprovante devolvido nesta transacao nao imprime linha de financiamento.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>R$ 1.000,01 credito: NEGADA 01 (tambem 167524 no debito)</t>
+          <t>Venda de R$ 1.000,01 no credito, recusada. Mensagem da adquirente: NEGADA 01 (campo mensagemRespostaAdquirente da intencao; em transacoes recusadas o PDV nao grava o dump bruto).</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Esc no menu de rede: OPERACAO CANCELADA</t>
+          <t>Operacao interrompida pelo operador na selecao de rede do PayGo: retorno OPERACAO CANCELADA e venda nao concluida.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Venda credito aprovada (consultada no passo 49)</t>
+          <t>Venda no credito de R$ 2,00, aprovada. 030-000 = TRANSACAO AUTORIZADA, 040-000 = MASTERCARD CREDITO, autorizacao 094787, NSU 741678. Mesma intencao consultada no passo 49.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Venda debito aprovada</t>
+          <t>Venda no debito de R$ 12,00, aprovada. 030-000 = TRANSACAO AUTORIZADA, 040-000 = VISA ELECTRON, autorizacao 094787, NSU 741672.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -997,8 +997,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>167563</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Venda no credito parcelada pela loja em 99 parcelas (quantidadeParcelas = 99, parcelamentoAdmin = false), R$ 990,00, aprovada. 030-000 = TRANSACAO AUTORIZADA, autorizacao 094787, NSU 742421. O comprovante devolvido nesta transacao nao imprime linha de parcelamento.</t>
+        </is>
+      </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Venda financiamento</t>
@@ -1035,8 +1043,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="5" t="n"/>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>167564</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Vias diferenciadas recebidas e impressas em separado: 713-* (Via Cliente) e 715-* (Via Estabelecimento), alem da via completa 029-*. Venda de R$ 10,00 no credito aprovada, NSU 742424.</t>
+        </is>
+      </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Recibos diferenciados</t>
@@ -1061,7 +1077,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Pix QR (PIX C6 BANK), aprovacao automatica</t>
+          <t>Venda Pix por QR Code aprovada, R$ 12,00. 030-000 = TRANSACAO AUTORIZADA, 010-000 = PIX C6 BANK, identificador ponta a ponta E1928374620260821213986g6pAvf343.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1184,8 +1200,16 @@
           <t>OPCIONAL</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="5" t="n"/>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>167566</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Venda de R$ 1,00 no credito aprovada, para uso no teste de cancelamento do passo 22. Autorizacao 094787, NSU 742427.</t>
+        </is>
+      </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
           <t>Vendas para testes de cancelamento</t>
@@ -1203,8 +1227,16 @@
           <t>OPCIONAL</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="5" t="n"/>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>167567</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Venda de R$ 2,00 no credito aprovada, para uso no teste de cancelamento do passo 20. Autorizacao 094787, NSU 742429.</t>
+        </is>
+      </c>
       <c r="E29" s="33" t="n"/>
     </row>
     <row r="30">
@@ -1218,8 +1250,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="5" t="n"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>167572</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Venda de R$ 12.345,67 no credito, aprovada. 030-000 = TRANSACAO AUTORIZADA, autorizacao 297061, NSU 682424.</t>
+        </is>
+      </c>
       <c r="E30" s="34" t="n"/>
     </row>
     <row r="31">
@@ -1233,8 +1273,16 @@
           <t>OPCIONAL</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="5" t="n"/>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>167567</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Cancelamento da venda do passo 18, aprovado. 030-000 = TRANSACAO AUTORIZADA. Comprovante: ESTORNO:742429 VALOR:R$ 2,00. NSU do estorno 44.</t>
+        </is>
+      </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Cancelamento</t>
@@ -1252,8 +1300,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="5" t="n"/>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>167572</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Cancelamento da venda do passo 19, aprovado. 030-000 = TRANSACAO AUTORIZADA. Comprovante: ***CANCELAMENTO*** / CANCELAMENTO DE VENDA / VALOR FINAL R$ 12.345,67. NSU do estorno 6.</t>
+        </is>
+      </c>
       <c r="E32" s="33" t="n"/>
     </row>
     <row r="33">
@@ -1267,8 +1323,16 @@
           <t>OPCIONAL</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="5" t="n"/>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>167566</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Cancelamento da venda do passo 17, aprovado. 030-000 = TRANSACAO AUTORIZADA. Comprovante: ESTORNO:742427 VALOR:R$ 1,00. NSU do estorno 46.</t>
+        </is>
+      </c>
       <c r="E33" s="33" t="n"/>
     </row>
     <row r="34">
@@ -1423,8 +1487,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>167575</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Mensagem de resultado no tamanho maximo recebida e exibida integralmente. 030-000 = TRANSACAO DE TESTE APROVADA. CODIGO AUTORIZACAO 13456789 TRANSACAO NAO PRODUTIVA (80 caracteres).</t>
+        </is>
+      </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
           <t>Msg tamanho máximo</t>
@@ -1732,8 +1804,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="5" t="n"/>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>167576</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Venda por aproximacao aprovada, R$ 1.020,00 no credito. 030-000 = TRANSACAO AUTORIZADA, autorizacao 094787, NSU 742439. Via com TRANSACAO AUTORIZADA MEDIANTE USO DE SENHA PESSOAL.</t>
+        </is>
+      </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
           <t>Venda por aproximção</t>
@@ -1751,8 +1831,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="5" t="n"/>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>167577</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Venda por aproximacao aprovada sem solicitacao de senha, R$ 999,00 no credito. 030-000 = TRANSACAO AUTORIZADA, autorizacao 387617, NSU 882826. As vias 713-* e 715-* nao contem USO DE SENHA PESSOAL nem TRANSACAO AUTORIZADA COM SENHA.</t>
+        </is>
+      </c>
       <c r="E57" s="34" t="n"/>
     </row>
     <row r="58">
@@ -1904,8 +1992,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="5" t="n"/>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>167560</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Venda Pix de R$ 500,00 aprovada. 030-000 = TRANSACAO AUTORIZADA, 010-000 = PIX C6 BANK, identificador ponta a ponta E19283746202608241411Pmggfpq7Cbr.</t>
+        </is>
+      </c>
       <c r="E64" s="33" t="n"/>
     </row>
     <row r="65">
@@ -1919,8 +2015,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="5" t="n"/>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>167560</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Cancelamento da venda Pix do passo 53 NEGADO pelo emissor, conforme esperado para este teste: TRANSACAO NEGADA PELO HOST.</t>
+        </is>
+      </c>
       <c r="E65" s="33" t="n"/>
     </row>
     <row r="66">

--- a/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
+++ b/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E66"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1796875" defaultRowHeight="15.5"/>
   <cols>
     <col width="12.54296875" customWidth="1" style="1" min="1" max="1"/>
@@ -700,6 +700,7 @@
     <col width="9.1796875" customWidth="1" style="1" min="6" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
@@ -1361,8 +1362,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="5" t="n"/>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>167602</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Queda de energia durante a venda: PC desligado no botao quando o pinpad pediu o cartao. Ao religar, a reconciliacao fechou a linha como recusado ("religamento: Pagamento Recusado"); nenhuma venda foi gravada (venda_id NULL). Nunca ficou paga.</t>
+        </is>
+      </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Queda energia</t>
@@ -1929,12 +1938,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>200 OK</t>
+          <t>167572</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Callback/Insert tipo 1 UrlRetorno -&gt; https://erp.americandaybrasil.com.br/paygo-callback</t>
+          <t>Callback/Insert cadastrado (200 OK) para https://erp.americandaybrasil.com.br/paygo-callback e POSTs RECEBIDOS: 33 notificacoes da PayGo (origem 191.232.70.197) em 24/08/2026, cada uma com intencaoVendaId na query. Evidencia em p50-callbacks-recebidos.log. Exemplos: 167572 (passo 19), 167575 (passo 30), 167576 (passo 45), 167577 (passo 46), 167598 (passo 52), 167602 (passo 24). Observacao: a venda do passo 06 (167513) e anterior ao cadastro da URL, por isso nao gerou callback.</t>
         </is>
       </c>
       <c r="E61" s="34" t="n"/>
@@ -1973,8 +1982,16 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="5" t="n"/>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>167598</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Venda PIX de R$ 500,00 com Esc na tela do QR: OPERACAO CANCELADA.</t>
+        </is>
+      </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
           <t>QR Code</t>

--- a/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
+++ b/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
@@ -838,12 +838,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>167517</t>
+          <t>167656</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Venda de R$ 100.000,00 (valor maximo da automacao) no credito, aprovada. 030-000 = TRANSACAO AUTORIZADA, autorizacao 094787, NSU 741684.</t>
+          <t>Venda de R$ 100.000,00 no credito, aprovada. E o maior valor que a automacao aceita.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>167518</t>
+          <t>167593</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Venda a vista de R$ 5,00 no credito, aprovada (quantidadeParcelas = 1 e aVista = true na intencao). 030-000 = TRANSACAO AUTORIZADA, autorizacao 094787, NSU 741686. O comprovante devolvido nesta transacao nao imprime linha de financiamento.</t>
+          <t>Venda a vista de R$ 5,00 no credito, aprovada. O comprovante traz a linha VENDA CREDITO A VISTA.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>167523</t>
+          <t>167657</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Venda de R$ 1.000,01 no credito, recusada. Mensagem da adquirente: NEGADA 01 (campo mensagemRespostaAdquirente da intencao; em transacoes recusadas o PDV nao grava o dump bruto).</t>
+          <t>Venda de R$ 1.000,01 no credito: negada, com a mensagem NEGADA 01 na tela do operador.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>167516</t>
+          <t>167661</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Operacao interrompida pelo operador na selecao de rede do PayGo: retorno OPERACAO CANCELADA e venda nao concluida.</t>
+          <t>Venda de R$ 8,99 no credito com Esc no menu de selecao de rede do PayGo: a operacao voltou cancelada, com a mensagem OPERACAO CANCELADA na tela do operador.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>167513</t>
+          <t>167658</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Venda no credito de R$ 2,00, aprovada. 030-000 = TRANSACAO AUTORIZADA, 040-000 = MASTERCARD CREDITO, autorizacao 094787, NSU 741678. Mesma intencao consultada no passo 49.</t>
+          <t>Venda de R$ 10,00 no credito, aprovada. E a venda consultada no passo 49 e notificada no callback do passo 50.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>167509</t>
+          <t>167659</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Venda no debito de R$ 12,00, aprovada. 030-000 = TRANSACAO AUTORIZADA, 040-000 = VISA ELECTRON, autorizacao 094787, NSU 741672.</t>
+          <t>Venda de R$ 10,00 no debito, aprovada.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>167563</t>
+          <t>167594</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Venda no credito parcelada pela loja em 99 parcelas (quantidadeParcelas = 99, parcelamentoAdmin = false), R$ 990,00, aprovada. 030-000 = TRANSACAO AUTORIZADA, autorizacao 094787, NSU 742421. O comprovante devolvido nesta transacao nao imprime linha de parcelamento.</t>
+          <t>Venda de R$ 990,00 no credito parcelada pela loja em 99 vezes, aprovada. O comprovante traz VENDA PARCELADA EM 99 VEZES SEM JUROS.</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>167564</t>
+          <t>167595</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Vias diferenciadas recebidas e impressas em separado: 713-* (Via Cliente) e 715-* (Via Estabelecimento), alem da via completa 029-*. Venda de R$ 10,00 no credito aprovada, NSU 742424.</t>
+          <t>Venda de R$ 10,00 no credito. As duas vias saem diferentes: a do estabelecimento tem uma linha a mais, com o criptograma EMV (ARQC), que nao aparece na via do cliente.</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>167507</t>
+          <t>167660</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Venda Pix por QR Code aprovada, R$ 12,00. 030-000 = TRANSACAO AUTORIZADA, 010-000 = PIX C6 BANK, identificador ponta a ponta E1928374620260821213986g6pAvf343.</t>
+          <t>Venda de R$ 10,00 no Pix (rede PIX C6 BANK). QR exibido na tela e aprovacao automatica.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Venda de R$ 1,00 no credito aprovada, para uso no teste de cancelamento do passo 22. Autorizacao 094787, NSU 742427.</t>
+          <t>Venda de R$ 1,00 no credito, aprovada, para ser cancelada no passo 22.</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Venda de R$ 2,00 no credito aprovada, para uso no teste de cancelamento do passo 20. Autorizacao 094787, NSU 742429.</t>
+          <t>Venda de R$ 2,00 no credito, aprovada, para ser cancelada no passo 20.</t>
         </is>
       </c>
       <c r="E29" s="33" t="n"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Venda de R$ 12.345,67 no credito, aprovada. 030-000 = TRANSACAO AUTORIZADA, autorizacao 297061, NSU 682424.</t>
+          <t>Venda de R$ 12.345,67 no credito, aprovada, para ser cancelada no passo 21.</t>
         </is>
       </c>
       <c r="E30" s="34" t="n"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Cancelamento da venda do passo 18, aprovado. 030-000 = TRANSACAO AUTORIZADA. Comprovante: ESTORNO:742429 VALOR:R$ 2,00. NSU do estorno 44.</t>
+          <t>Cancelamento da venda do passo 18 (R$ 2,00), aprovado, com comprovante de estorno.</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Cancelamento da venda do passo 19, aprovado. 030-000 = TRANSACAO AUTORIZADA. Comprovante: ***CANCELAMENTO*** / CANCELAMENTO DE VENDA / VALOR FINAL R$ 12.345,67. NSU do estorno 6.</t>
+          <t>Cancelamento da venda do passo 19 (R$ 12.345,67), aprovado, com comprovante de estorno.</t>
         </is>
       </c>
       <c r="E32" s="33" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Cancelamento da venda do passo 17, aprovado. 030-000 = TRANSACAO AUTORIZADA. Comprovante: ESTORNO:742427 VALOR:R$ 1,00. NSU do estorno 46.</t>
+          <t>Cancelamento da venda do passo 17 (R$ 1,00), aprovado, com comprovante de estorno.</t>
         </is>
       </c>
       <c r="E33" s="33" t="n"/>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Queda de energia durante a venda: PC desligado no botao quando o pinpad pediu o cartao. Ao religar, a reconciliacao fechou a linha como recusado ("religamento: Pagamento Recusado"); nenhuma venda foi gravada (venda_id NULL). Nunca ficou paga.</t>
+          <t>Queda de energia durante a venda de R$ 500,00: o PC foi desligado no botao quando o pinpad pediu o cartao. Ao religar, o PDV consultou a intencao e fechou a linha como recusada. Nenhuma venda foi gravada e a cobranca nunca ficou paga.</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Mensagem de resultado no tamanho maximo recebida e exibida integralmente. 030-000 = TRANSACAO DE TESTE APROVADA. CODIGO AUTORIZACAO 13456789 TRANSACAO NAO PRODUTIVA (80 caracteres).</t>
+          <t>Venda de R$ 1.003,00 no credito, aprovada com a mensagem de tamanho maximo: TRANSACAO DE TESTE APROVADA. CODIGO AUTORIZACAO 13456789 TRANSACAO NAO PRODUTIVA, exibida por inteiro.</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>167576</t>
+          <t>167596</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Venda por aproximacao aprovada, R$ 1.020,00 no credito. 030-000 = TRANSACAO AUTORIZADA, autorizacao 094787, NSU 742439. Via com TRANSACAO AUTORIZADA MEDIANTE USO DE SENHA PESSOAL.</t>
+          <t>Venda de R$ 1.020,00 por aproximacao, aprovada. O pinpad pediu APROXIME, INSIRA OU PASSE.</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Venda por aproximacao aprovada sem solicitacao de senha, R$ 999,00 no credito. 030-000 = TRANSACAO AUTORIZADA, autorizacao 387617, NSU 882826. As vias 713-* e 715-* nao contem USO DE SENHA PESSOAL nem TRANSACAO AUTORIZADA COM SENHA.</t>
+          <t>Venda de R$ 999,00 por aproximacao, aprovada sem pedir senha. O comprovante nao traz a linha de uso de senha pessoal.</t>
         </is>
       </c>
       <c r="E57" s="34" t="n"/>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>167517</t>
+          <t>167656</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>IntencaoVenda/GetById da venda do passo 02: status 10 Creditado</t>
+          <t>IntencaoVenda/GetById da venda do passo 02: status 10 (Creditado), valor 100.000,00. JSON em p48-intencao-167656.json.</t>
         </is>
       </c>
       <c r="E59" s="33" t="n"/>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>167513</t>
+          <t>167658</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>IntencaoVenda/GetById da venda do passo 06: status 10 Creditado</t>
+          <t>IntencaoVenda/GetById da venda do passo 06: status 10 (Creditado), valor 10,00. JSON em p49-intencao-167658.json.</t>
         </is>
       </c>
       <c r="E60" s="33" t="n"/>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>167572</t>
+          <t>167658</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Callback/Insert cadastrado (200 OK) para https://erp.americandaybrasil.com.br/paygo-callback e POSTs RECEBIDOS: 33 notificacoes da PayGo (origem 191.232.70.197) em 24/08/2026, cada uma com intencaoVendaId na query. Evidencia em p50-callbacks-recebidos.log. Exemplos: 167572 (passo 19), 167575 (passo 30), 167576 (passo 45), 167577 (passo 46), 167598 (passo 52), 167602 (passo 24). Observacao: a venda do passo 06 (167513) e anterior ao cadastro da URL, por isso nao gerou callback.</t>
+          <t>Callback/Insert cadastrado (200 OK) e POST recebido. A venda do passo 06 gerou a notificacao em 24/08 as 17:12:15, com o intencaoVendaId na query. Log completo em p50-callbacks-recebidos.log, com 38 notificacoes recebidas no total.</t>
         </is>
       </c>
       <c r="E61" s="34" t="n"/>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Venda PIX de R$ 500,00 com Esc na tela do QR: OPERACAO CANCELADA.</t>
+          <t>Venda de R$ 500,00 no Pix com Esc na tela do QR: OPERACAO CANCELADA.</t>
         </is>
       </c>
       <c r="E63" s="21" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Venda Pix de R$ 500,00 aprovada. 030-000 = TRANSACAO AUTORIZADA, 010-000 = PIX C6 BANK, identificador ponta a ponta E19283746202608241411Pmggfpq7Cbr.</t>
+          <t>Venda de R$ 500,00 no Pix (rede PIX C6 BANK), aprovada.</t>
         </is>
       </c>
       <c r="E64" s="33" t="n"/>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Cancelamento da venda Pix do passo 53 NEGADO pelo emissor, conforme esperado para este teste: TRANSACAO NEGADA PELO HOST.</t>
+          <t>Tentativa de cancelar a venda do passo 53: negada pelo host, que e o resultado esperado para cancelamento de Pix.</t>
         </is>
       </c>
       <c r="E65" s="33" t="n"/>

--- a/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
+++ b/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Tentativa de cancelar a venda do passo 53: negada pelo host, que e o resultado esperado para cancelamento de Pix.</t>
+          <t>Tentativa de cancelar a venda do passo 53 (Pix): NEGADA. A consulta da intencao 167560 mostra os dois pagamentos externos: TRANSACAO AUTORIZADA na venda e TRANSACAO NEGADA PELO HOST no cancelamento. A venda segue creditada. E o resultado esperado para cancelamento de Pix. JSON em p54-cancelamento-negado-167560.json.</t>
         </is>
       </c>
       <c r="E65" s="33" t="n"/>

--- a/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
+++ b/docs/evidencias-controlpay/Planilha de testes v20260703 - PREENCHIDA.xlsx
@@ -946,12 +946,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>167658</t>
+          <t>167726</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Venda de R$ 10,00 no credito, aprovada. E a venda consultada no passo 49 e notificada no callback do passo 50.</t>
+          <t>Venda de R$ 10,00 no credito, com o cartao INSERIDO no chip (adquirente C6 PAY). O comprovante traz o prefixo C- na linha do cartao, que identifica a leitura por chip. E a venda consultada no passo 49 e notificada no callback do passo 50.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>167659</t>
+          <t>167733</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Venda de R$ 10,00 no debito, aprovada.</t>
+          <t>Venda de R$ 10,00 no debito, com o cartao INSERIDO no chip (adquirente C6 PAY). O comprovante traz o prefixo C- na linha do cartao.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>167566</t>
+          <t>167730</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Venda de R$ 1,00 no credito, aprovada, para ser cancelada no passo 22.</t>
+          <t>Venda de R$ 1,00 no credito pela adquirente C6 PAY, aprovada, para ser cancelada no passo 22.</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>167567</t>
+          <t>167731</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Venda de R$ 2,00 no credito, aprovada, para ser cancelada no passo 20.</t>
+          <t>Venda de R$ 2,00 no credito pela adquirente C6 PAY, aprovada, para ser cancelada no passo 20.</t>
         </is>
       </c>
       <c r="E29" s="33" t="n"/>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>167567</t>
+          <t>167731</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Cancelamento da venda do passo 18 (R$ 2,00), aprovado, com comprovante de estorno.</t>
+          <t>Cancelamento da venda do passo 18 (R$ 2,00, C6 PAY), aprovado, com comprovante de estorno.</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>167566</t>
+          <t>167730</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Cancelamento da venda do passo 17 (R$ 1,00), aprovado, com comprovante de estorno.</t>
+          <t>Cancelamento da venda do passo 17 (R$ 1,00, C6 PAY), aprovado, com comprovante de estorno.</t>
         </is>
       </c>
       <c r="E33" s="33" t="n"/>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>167658</t>
+          <t>167726</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>IntencaoVenda/GetById da venda do passo 06: status 10 (Creditado), valor 10,00. JSON em p49-intencao-167658.json.</t>
+          <t>IntencaoVenda/GetById da venda do passo 06: status 10 (Creditado), valor 10,00. JSON em p49-intencao-167726.json.</t>
         </is>
       </c>
       <c r="E60" s="33" t="n"/>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>167658</t>
+          <t>167726</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Callback/Insert cadastrado (200 OK) e POST recebido. A venda do passo 06 gerou a notificacao em 24/08 as 17:12:15, com o intencaoVendaId na query. Log completo em p50-callbacks-recebidos.log, com 38 notificacoes recebidas no total.</t>
+          <t>Callback/Insert cadastrado (200 OK) e POST recebido. A venda do passo 06 gerou a notificacao em 25/08 as 10:25:18, com o intencaoVendaId na query. Log completo em p50-callbacks-recebidos.log, com 49 notificacoes recebidas no total.</t>
         </is>
       </c>
       <c r="E61" s="34" t="n"/>
